--- a/salidas/REMPLAZADOS.xlsx
+++ b/salidas/REMPLAZADOS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AH2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,95 +464,125 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>correo_electronico_anterior</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>foto_1_path_anterior</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>foto_2_path_anterior</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>calle_anterior</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>numero_anterior</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>manzana_inegi_anterior</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>manzana_anterior</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>lote_anterior</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>curp_anterior</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>coordenadas_gps_anterior</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>direccion_base_anterior</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>nombre_nuevo</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>edad_nueva</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>telefono_nuevo</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>correo_electronico_nuevo</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>foto_1_path_nuevo</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>foto_2_path_nuevo</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
         <is>
           <t>calle_nueva</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>numero_nuevo</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>manzana_inegi_nueva</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>manzana_nueva</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>lote_nuevo</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>curp_nuevo</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>coordenadas_gps_nueva</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>direccion_base_nueva</t>
         </is>
@@ -606,79 +636,109 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>lulu50</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fotos/ines_pacheco/device-z9p72n/1773076886443-evkzq_1.jpg</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>fotos/ines_pacheco/device-z9p72n/1773076886443-evkzq_2.jpg</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>Etta</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>11453005</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
+          <t>11453005</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>Sosjdidkmflfll</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>19.389573,-99.195197</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Calle: Etta mz. 2 num int: lote 3 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>lourdes</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>5555555552</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>lulu50@gmail.com</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>fotos/ines_pacheco/device-z9p72n/1773076886443-evkzq_1.jpg</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>fotos/ines_pacheco/device-z9p72n/1773076886443-evkzq_2.jpg</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Etta</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr">
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
         <is>
           <t>11453005</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr">
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Sosjdidkmflfll</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>19.389573,-99.195197</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>Calle: Etta mz. 2 num int: lote 3 Col: Lomas de Becerra S1</t>
         </is>

--- a/salidas/REMPLAZADOS.xlsx
+++ b/salidas/REMPLAZADOS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,110 +479,140 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>foto_3_path_anterior</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>calle_anterior</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>numero_anterior</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>manzana_inegi_anterior</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>manzana_anterior</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>lote_anterior</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>curp_anterior</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>colonia_anterior</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>codigo_postal_anterior</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>coordenadas_gps_anterior</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>direccion_base_anterior</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>nombre_nuevo</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>edad_nueva</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>telefono_nuevo</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>correo_electronico_nuevo</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>foto_1_path_nuevo</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>foto_2_path_nuevo</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>foto_3_path_nuevo</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>calle_nueva</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>numero_nuevo</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>manzana_inegi_nueva</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>manzana_nueva</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>lote_nuevo</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>curp_nuevo</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>colonia_nueva</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>codigo_postal_nueva</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
         <is>
           <t>coordenadas_gps_nueva</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>direccion_base_nueva</t>
         </is>
@@ -649,96 +679,102 @@
           <t>fotos/ines_pacheco/device-z9p72n/1773076886443-evkzq_2.jpg</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Etta</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>11453005</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>Sosjdidkmflfll</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
         <is>
           <t>19.389573,-99.195197</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Calle: Etta mz. 2 num int: lote 3 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>lourdes</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>5555555552</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>lulu50@gmail.com</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>fotos/ines_pacheco/device-z9p72n/1773076886443-evkzq_1.jpg</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>fotos/ines_pacheco/device-z9p72n/1773076886443-evkzq_2.jpg</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Etta</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>11453005</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr">
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>Sosjdidkmflfll</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr">
         <is>
           <t>19.389573,-99.195197</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>Calle: Etta mz. 2 num int: lote 3 Col: Lomas de Becerra S1</t>
         </is>

--- a/salidas/REMPLAZADOS.xlsx
+++ b/salidas/REMPLAZADOS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -777,6 +777,208 @@
       <c r="AN2" t="inlineStr">
         <is>
           <t>Calle: Etta mz. 2 num int: lote 3 Col: Lomas de Becerra S1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1773085735134-vyrp3k</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-09T19:48:55.134Z</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3041784</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FREDY FLORES NAHUACATL</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1773085006116-18aeo</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1773085006116-18aeo</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cynthya Kraouss Vilchis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5566778899</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ajhgdhhd@jjajaye.com</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FDDOKNWUURE787163G_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FDDOKNWUURE787163G_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FDDOKNWUURE787163G_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Canario</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>12216012</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Qer</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>FDDOKNWUURE787163G</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>TOLTECA</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>08173</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>19.389542,-99.195124</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Calle: Savi 4 num int: 145 Col: Pueblo Santa Lucia</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Cynthya Kraouss Vilchis</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>5566778833</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>ajugdgydte@aisuuew.com</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FEOIBA88723JAIIHDHS_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FEOIBA88723JAIIHDHS_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FEOIBA88723JAIIHDHS_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Canario</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>12216012</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>FEOIBA88723JAIIHDHS</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>TOLTECA</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>09812</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>19.389542,-99.195124</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>Calle: Savi 4 num int: 145 Col: Pueblo Santa Lucia</t>
         </is>
       </c>
     </row>

--- a/salidas/REMPLAZADOS.xlsx
+++ b/salidas/REMPLAZADOS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AP3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,95 +524,105 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>descripcion_vivienda_anterior</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>coordenadas_gps_anterior</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>direccion_base_anterior</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>nombre_nuevo</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>edad_nueva</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>telefono_nuevo</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>correo_electronico_nuevo</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>foto_1_path_nuevo</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>foto_2_path_nuevo</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>foto_3_path_nuevo</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>calle_nueva</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>numero_nuevo</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>manzana_inegi_nueva</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>manzana_nueva</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>lote_nuevo</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>curp_nuevo</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>colonia_nueva</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>codigo_postal_nueva</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>descripcion_vivienda_nueva</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
         <is>
           <t>coordenadas_gps_nueva</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>direccion_base_nueva</t>
         </is>
@@ -704,77 +714,79 @@
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
         <is>
           <t>19.389573,-99.195197</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Calle: Etta mz. 2 num int: lote 3 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>lourdes</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>5555555552</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>lulu50@gmail.com</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>fotos/ines_pacheco/device-z9p72n/1773076886443-evkzq_1.jpg</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>fotos/ines_pacheco/device-z9p72n/1773076886443-evkzq_2.jpg</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Etta</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr">
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>11453005</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr">
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>Sosjdidkmflfll</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr">
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>19.389573,-99.195197</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>Calle: Etta mz. 2 num int: lote 3 Col: Lomas de Becerra S1</t>
         </is>
@@ -886,97 +898,99 @@
           <t>08173</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
         <is>
           <t>19.389542,-99.195124</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Calle: Savi 4 num int: 145 Col: Pueblo Santa Lucia</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Cynthya Kraouss Vilchis</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>5566778833</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>ajugdgydte@aisuuew.com</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FEOIBA88723JAIIHDHS_frontal.jpg</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FEOIBA88723JAIIHDHS_reverso.jpg</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FEOIBA88723JAIIHDHS_comprobante.jpg</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>Canario</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>12216012</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>FEOIBA88723JAIIHDHS</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>TOLTECA</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>09812</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>19.389542,-99.195124</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>Calle: Savi 4 num int: 145 Col: Pueblo Santa Lucia</t>
         </is>

--- a/salidas/REMPLAZADOS.xlsx
+++ b/salidas/REMPLAZADOS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP3"/>
+  <dimension ref="A1:AP1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,374 +625,6 @@
       <c r="AP1" t="inlineStr">
         <is>
           <t>direccion_base_nueva</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1773076961529-z5ascw</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-09T17:22:41.529Z</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3060955</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>INES PACHECO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1773076886443-evkzq</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1773076886443-evkzq</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>lourdes</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5555555552</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>lulu50</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fotos/ines_pacheco/device-z9p72n/1773076886443-evkzq_1.jpg</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>fotos/ines_pacheco/device-z9p72n/1773076886443-evkzq_2.jpg</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Etta</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>11453005</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Sosjdidkmflfll</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>19.389573,-99.195197</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Calle: Etta mz. 2 num int: lote 3 Col: Lomas de Becerra S1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>lourdes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>5555555552</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lulu50@gmail.com</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>fotos/ines_pacheco/device-z9p72n/1773076886443-evkzq_1.jpg</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>fotos/ines_pacheco/device-z9p72n/1773076886443-evkzq_2.jpg</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>Etta</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>11453005</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Sosjdidkmflfll</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>19.389573,-99.195197</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Calle: Etta mz. 2 num int: lote 3 Col: Lomas de Becerra S1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1773085735134-vyrp3k</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-09T19:48:55.134Z</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3041784</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>FREDY FLORES NAHUACATL</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1773085006116-18aeo</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1773085006116-18aeo</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Cynthya Kraouss Vilchis</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5566778899</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ajhgdhhd@jjajaye.com</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FDDOKNWUURE787163G_frontal.jpg</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FDDOKNWUURE787163G_reverso.jpg</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FDDOKNWUURE787163G_comprobante.jpg</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Canario</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>12216012</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Qer</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>FDDOKNWUURE787163G</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>TOLTECA</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>08173</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>19.389542,-99.195124</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Calle: Savi 4 num int: 145 Col: Pueblo Santa Lucia</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Cynthya Kraouss Vilchis</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>5566778833</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>ajugdgydte@aisuuew.com</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FEOIBA88723JAIIHDHS_frontal.jpg</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FEOIBA88723JAIIHDHS_reverso.jpg</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FEOIBA88723JAIIHDHS_comprobante.jpg</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>Canario</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>12216012</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>FEOIBA88723JAIIHDHS</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>TOLTECA</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>09812</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>19.389542,-99.195124</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Calle: Savi 4 num int: 145 Col: Pueblo Santa Lucia</t>
         </is>
       </c>
     </row>

--- a/salidas/REMPLAZADOS.xlsx
+++ b/salidas/REMPLAZADOS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP1"/>
+  <dimension ref="A1:BB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,175 +454,235 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>nombre_base_anterior</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>apellido_paterno_anterior</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>apellido_materno_anterior</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>edad_anterior</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>telefono_anterior</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>correo_electronico_anterior</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>foto_1_path_anterior</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>foto_1_url_anterior</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>foto_2_path_anterior</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>foto_2_url_anterior</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>foto_3_path_anterior</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>foto_3_url_anterior</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
         <is>
           <t>calle_anterior</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>numero_anterior</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>manzana_inegi_anterior</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>manzana_anterior</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>lote_anterior</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>curp_anterior</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>colonia_anterior</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>codigo_postal_anterior</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>descripcion_vivienda_anterior</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>coordenadas_gps_anterior</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>direccion_base_anterior</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>nombre_nuevo</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>nombre_base_nuevo</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>apellido_paterno_nuevo</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>apellido_materno_nuevo</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
         <is>
           <t>edad_nueva</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>telefono_nuevo</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>correo_electronico_nuevo</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>foto_1_path_nuevo</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>foto_1_url_nuevo</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
         <is>
           <t>foto_2_path_nuevo</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>foto_2_url_nuevo</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
         <is>
           <t>foto_3_path_nuevo</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>foto_3_url_nuevo</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
         <is>
           <t>calle_nueva</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>numero_nuevo</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>manzana_inegi_nueva</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>manzana_nueva</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>lote_nuevo</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>curp_nuevo</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>colonia_nueva</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>codigo_postal_nueva</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>descripcion_vivienda_nueva</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>coordenadas_gps_nueva</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>direccion_base_nueva</t>
         </is>
